--- a/Scripts_annehuitema2003/data_output/GP3_improvements_25-24_sessions/income_ratio_satis_plot/Session_240924/vjcortesa_spendshare_meanplayers_S240924_Round_1_Gall_Pall.xlsx
+++ b/Scripts_annehuitema2003/data_output/GP3_improvements_25-24_sessions/income_ratio_satis_plot/Session_240924/vjcortesa_spendshare_meanplayers_S240924_Round_1_Gall_Pall.xlsx
@@ -530,13 +530,13 @@
         <v>56.48604269293924</v>
       </c>
       <c r="F6">
-        <v>4.4</v>
+        <v>4.363636363636363</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
-        <v>25.80645161290323</v>
+        <v>24.63343108504397</v>
       </c>
     </row>
     <row r="7">
@@ -2192,10 +2192,10 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>40000</v>
+        <v>160000</v>
       </c>
       <c r="E65">
-        <v>40000</v>
+        <v>160000</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>25.80645161290323</v>
+        <v>24.63343108504397</v>
       </c>
       <c r="D6">
-        <v>4.4</v>
+        <v>4.363636363636363</v>
       </c>
     </row>
     <row r="7">
